--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700114</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127700117</v>
       </c>
       <c r="B3" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>91951</v>
+        <v>91953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127700131</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700126</v>
+        <v>127700145</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>78426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729396</v>
+        <v>729180</v>
       </c>
       <c r="R6" t="n">
-        <v>7171606</v>
+        <v>7171769</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700145</v>
+        <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>78424</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729180</v>
+        <v>729396</v>
       </c>
       <c r="R7" t="n">
-        <v>7171769</v>
+        <v>7171606</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127700138</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127700139</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91280</v>
+        <v>91282</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127700118</v>
       </c>
       <c r="B12" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700143</v>
+        <v>127700116</v>
       </c>
       <c r="B15" t="n">
-        <v>92620</v>
+        <v>80159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729196</v>
+        <v>729372</v>
       </c>
       <c r="R15" t="n">
-        <v>7171782</v>
+        <v>7171627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700116</v>
+        <v>127700143</v>
       </c>
       <c r="B16" t="n">
-        <v>80157</v>
+        <v>92622</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729372</v>
+        <v>729196</v>
       </c>
       <c r="R16" t="n">
-        <v>7171627</v>
+        <v>7171782</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700111</v>
+        <v>127700108</v>
       </c>
       <c r="B17" t="n">
-        <v>92813</v>
+        <v>57660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,34 +2141,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Krokänget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729181</v>
+        <v>729279</v>
       </c>
       <c r="R17" t="n">
-        <v>7171786</v>
+        <v>7171575</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2201,6 +2209,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,10 +2240,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700108</v>
+        <v>127700111</v>
       </c>
       <c r="B18" t="n">
-        <v>57658</v>
+        <v>92815</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,42 +2251,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Krokänget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729279</v>
+        <v>729181</v>
       </c>
       <c r="R18" t="n">
-        <v>7171575</v>
+        <v>7171786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2306,11 +2311,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700145</v>
+        <v>127700125</v>
       </c>
       <c r="B6" t="n">
-        <v>78426</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729180</v>
+        <v>729406</v>
       </c>
       <c r="R6" t="n">
-        <v>7171769</v>
+        <v>7171499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127700125</v>
+        <v>127700145</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>78426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729406</v>
+        <v>729180</v>
       </c>
       <c r="R8" t="n">
-        <v>7171499</v>
+        <v>7171769</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700116</v>
+        <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>80159</v>
+        <v>92622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729372</v>
+        <v>729196</v>
       </c>
       <c r="R15" t="n">
-        <v>7171627</v>
+        <v>7171782</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700143</v>
+        <v>127700116</v>
       </c>
       <c r="B16" t="n">
-        <v>92622</v>
+        <v>80159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729196</v>
+        <v>729372</v>
       </c>
       <c r="R16" t="n">
-        <v>7171782</v>
+        <v>7171627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700108</v>
+        <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>57660</v>
+        <v>92815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,42 +2141,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Krokänget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729279</v>
+        <v>729181</v>
       </c>
       <c r="R17" t="n">
-        <v>7171575</v>
+        <v>7171786</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2209,11 +2201,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2240,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700111</v>
+        <v>127700108</v>
       </c>
       <c r="B18" t="n">
-        <v>92815</v>
+        <v>57660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2251,34 +2238,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Krokänget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729181</v>
+        <v>729279</v>
       </c>
       <c r="R18" t="n">
-        <v>7171786</v>
+        <v>7171575</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2311,6 +2306,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700125</v>
+        <v>127700126</v>
       </c>
       <c r="B6" t="n">
         <v>91350</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729406</v>
+        <v>729396</v>
       </c>
       <c r="R6" t="n">
-        <v>7171499</v>
+        <v>7171606</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700126</v>
+        <v>127700125</v>
       </c>
       <c r="B7" t="n">
         <v>91350</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729396</v>
+        <v>729406</v>
       </c>
       <c r="R7" t="n">
-        <v>7171606</v>
+        <v>7171499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>91953</v>
+        <v>91959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127700126</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127700125</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91282</v>
+        <v>91288</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700114</v>
       </c>
       <c r="B2" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127700117</v>
       </c>
       <c r="B3" t="n">
-        <v>80159</v>
+        <v>80162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>91959</v>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127700131</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700126</v>
+        <v>127700145</v>
       </c>
       <c r="B6" t="n">
-        <v>91356</v>
+        <v>78429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729396</v>
+        <v>729180</v>
       </c>
       <c r="R6" t="n">
-        <v>7171606</v>
+        <v>7171769</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700125</v>
+        <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729406</v>
+        <v>729396</v>
       </c>
       <c r="R7" t="n">
-        <v>7171499</v>
+        <v>7171606</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127700145</v>
+        <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>78426</v>
+        <v>91359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729180</v>
+        <v>729406</v>
       </c>
       <c r="R8" t="n">
-        <v>7171769</v>
+        <v>7171499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>127700138</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127700139</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91288</v>
+        <v>91291</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127700118</v>
       </c>
       <c r="B12" t="n">
-        <v>80159</v>
+        <v>80162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700143</v>
+        <v>127700116</v>
       </c>
       <c r="B15" t="n">
-        <v>92628</v>
+        <v>80162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729196</v>
+        <v>729372</v>
       </c>
       <c r="R15" t="n">
-        <v>7171782</v>
+        <v>7171627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700116</v>
+        <v>127700143</v>
       </c>
       <c r="B16" t="n">
-        <v>80159</v>
+        <v>92631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729372</v>
+        <v>729196</v>
       </c>
       <c r="R16" t="n">
-        <v>7171627</v>
+        <v>7171782</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>127700108</v>
       </c>
       <c r="B18" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700114</v>
       </c>
       <c r="B2" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127700117</v>
       </c>
       <c r="B3" t="n">
-        <v>80162</v>
+        <v>80168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>91962</v>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127700131</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700145</v>
+        <v>127700126</v>
       </c>
       <c r="B6" t="n">
-        <v>78429</v>
+        <v>91367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729180</v>
+        <v>729396</v>
       </c>
       <c r="R6" t="n">
-        <v>7171769</v>
+        <v>7171606</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700126</v>
+        <v>127700125</v>
       </c>
       <c r="B7" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729396</v>
+        <v>729406</v>
       </c>
       <c r="R7" t="n">
-        <v>7171606</v>
+        <v>7171499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127700125</v>
+        <v>127700145</v>
       </c>
       <c r="B8" t="n">
-        <v>91359</v>
+        <v>78435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729406</v>
+        <v>729180</v>
       </c>
       <c r="R8" t="n">
-        <v>7171499</v>
+        <v>7171769</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>127700138</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127700139</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91291</v>
+        <v>91299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127700118</v>
       </c>
       <c r="B12" t="n">
-        <v>80162</v>
+        <v>80168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700116</v>
+        <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>80162</v>
+        <v>92639</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729372</v>
+        <v>729196</v>
       </c>
       <c r="R15" t="n">
-        <v>7171627</v>
+        <v>7171782</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700143</v>
+        <v>127700116</v>
       </c>
       <c r="B16" t="n">
-        <v>92631</v>
+        <v>80168</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729196</v>
+        <v>729372</v>
       </c>
       <c r="R16" t="n">
-        <v>7171782</v>
+        <v>7171627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>127700108</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>91970</v>
+        <v>91971</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700126</v>
+        <v>127700145</v>
       </c>
       <c r="B6" t="n">
-        <v>91367</v>
+        <v>78435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729396</v>
+        <v>729180</v>
       </c>
       <c r="R6" t="n">
-        <v>7171606</v>
+        <v>7171769</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700125</v>
+        <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729406</v>
+        <v>729396</v>
       </c>
       <c r="R7" t="n">
-        <v>7171499</v>
+        <v>7171606</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127700145</v>
+        <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>78435</v>
+        <v>91368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729180</v>
+        <v>729406</v>
       </c>
       <c r="R8" t="n">
-        <v>7171769</v>
+        <v>7171499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>91300</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700111</v>
+        <v>127700108</v>
       </c>
       <c r="B17" t="n">
-        <v>92833</v>
+        <v>57669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,34 +2141,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Krokänget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729181</v>
+        <v>729279</v>
       </c>
       <c r="R17" t="n">
-        <v>7171786</v>
+        <v>7171575</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2201,6 +2209,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,10 +2240,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700108</v>
+        <v>127700111</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>92833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,42 +2251,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Krokänget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729279</v>
+        <v>729181</v>
       </c>
       <c r="R18" t="n">
-        <v>7171575</v>
+        <v>7171786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2306,11 +2311,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>91971</v>
+        <v>91972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91300</v>
+        <v>91301</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700108</v>
+        <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>57669</v>
+        <v>92834</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,42 +2141,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Krokänget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729279</v>
+        <v>729181</v>
       </c>
       <c r="R17" t="n">
-        <v>7171575</v>
+        <v>7171786</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2209,11 +2201,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2240,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700111</v>
+        <v>127700108</v>
       </c>
       <c r="B18" t="n">
-        <v>92833</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2251,34 +2238,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Krokänget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729181</v>
+        <v>729279</v>
       </c>
       <c r="R18" t="n">
-        <v>7171786</v>
+        <v>7171575</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2311,6 +2306,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>91972</v>
+        <v>91973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700145</v>
+        <v>127700126</v>
       </c>
       <c r="B6" t="n">
-        <v>78435</v>
+        <v>91370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729180</v>
+        <v>729396</v>
       </c>
       <c r="R6" t="n">
-        <v>7171769</v>
+        <v>7171606</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700126</v>
+        <v>127700125</v>
       </c>
       <c r="B7" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729396</v>
+        <v>729406</v>
       </c>
       <c r="R7" t="n">
-        <v>7171606</v>
+        <v>7171499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127700125</v>
+        <v>127700145</v>
       </c>
       <c r="B8" t="n">
-        <v>91369</v>
+        <v>78435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729406</v>
+        <v>729180</v>
       </c>
       <c r="R8" t="n">
-        <v>7171499</v>
+        <v>7171769</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91301</v>
+        <v>91302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>92834</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700114</v>
       </c>
       <c r="B2" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127700117</v>
       </c>
       <c r="B3" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>91973</v>
+        <v>91981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127700131</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127700126</v>
       </c>
       <c r="B6" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127700125</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127700145</v>
       </c>
       <c r="B8" t="n">
-        <v>78435</v>
+        <v>78438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127700138</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127700139</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91302</v>
+        <v>91310</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127700118</v>
       </c>
       <c r="B12" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700143</v>
+        <v>127700116</v>
       </c>
       <c r="B15" t="n">
-        <v>92642</v>
+        <v>80171</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729196</v>
+        <v>729372</v>
       </c>
       <c r="R15" t="n">
-        <v>7171782</v>
+        <v>7171627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700116</v>
+        <v>127700143</v>
       </c>
       <c r="B16" t="n">
-        <v>80168</v>
+        <v>92650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729372</v>
+        <v>729196</v>
       </c>
       <c r="R16" t="n">
-        <v>7171627</v>
+        <v>7171782</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>92843</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>127700108</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700114</v>
       </c>
       <c r="B2" t="n">
-        <v>80135</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127700117</v>
       </c>
       <c r="B3" t="n">
-        <v>80171</v>
+        <v>80182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>91981</v>
+        <v>91992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127700131</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700126</v>
+        <v>127700145</v>
       </c>
       <c r="B6" t="n">
-        <v>91378</v>
+        <v>78449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729396</v>
+        <v>729180</v>
       </c>
       <c r="R6" t="n">
-        <v>7171606</v>
+        <v>7171769</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127700125</v>
+        <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729406</v>
+        <v>729396</v>
       </c>
       <c r="R7" t="n">
-        <v>7171499</v>
+        <v>7171606</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127700145</v>
+        <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>78438</v>
+        <v>91389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729180</v>
+        <v>729406</v>
       </c>
       <c r="R8" t="n">
-        <v>7171769</v>
+        <v>7171499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>127700138</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127700139</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91310</v>
+        <v>91321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127700118</v>
       </c>
       <c r="B12" t="n">
-        <v>80171</v>
+        <v>80182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92650</v>
+        <v>92661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91378</v>
+        <v>91389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700116</v>
+        <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>80171</v>
+        <v>92661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729372</v>
+        <v>729196</v>
       </c>
       <c r="R15" t="n">
-        <v>7171627</v>
+        <v>7171782</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700143</v>
+        <v>127700116</v>
       </c>
       <c r="B16" t="n">
-        <v>92650</v>
+        <v>80182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729196</v>
+        <v>729372</v>
       </c>
       <c r="R16" t="n">
-        <v>7171782</v>
+        <v>7171627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>92843</v>
+        <v>92854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>127700108</v>
       </c>
       <c r="B18" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700114</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>80225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127700117</v>
       </c>
       <c r="B3" t="n">
-        <v>80182</v>
+        <v>80261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>91992</v>
+        <v>92125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,14 +970,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127700131</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,14 +1071,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127700145</v>
       </c>
       <c r="B6" t="n">
-        <v>78449</v>
+        <v>78523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,14 +1172,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91389</v>
+        <v>91522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,14 +1273,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91389</v>
+        <v>91522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,14 +1374,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127700138</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,14 +1475,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127700139</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,14 +1576,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91321</v>
+        <v>91454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,14 +1677,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>127700118</v>
       </c>
       <c r="B12" t="n">
-        <v>80182</v>
+        <v>80261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,14 +1778,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92661</v>
+        <v>92794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,14 +1879,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91389</v>
+        <v>91522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,14 +1980,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92661</v>
+        <v>92794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2029,14 +2081,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127700116</v>
       </c>
       <c r="B16" t="n">
-        <v>80182</v>
+        <v>80261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2126,14 +2182,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>92854</v>
+        <v>92989</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2223,14 +2283,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>127700108</v>
       </c>
       <c r="B18" t="n">
-        <v>57681</v>
+        <v>57713</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,7 +2397,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700114</v>
       </c>
       <c r="B2" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700117</v>
       </c>
       <c r="B3" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>92125</v>
+        <v>92129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127700131</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127700145</v>
       </c>
       <c r="B6" t="n">
-        <v>78523</v>
+        <v>78527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127700138</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127700139</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91454</v>
+        <v>91458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127700118</v>
       </c>
       <c r="B12" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>127700116</v>
       </c>
       <c r="B16" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>127700108</v>
       </c>
       <c r="B18" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700114</v>
       </c>
       <c r="B2" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700117</v>
       </c>
       <c r="B3" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>92129</v>
+        <v>92134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127700131</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127700145</v>
       </c>
       <c r="B6" t="n">
-        <v>78527</v>
+        <v>78432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127700138</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127700139</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91458</v>
+        <v>91463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127700118</v>
       </c>
       <c r="B12" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>127700116</v>
       </c>
       <c r="B16" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>127700108</v>
       </c>
       <c r="B18" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>92142</v>
+        <v>92147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91470</v>
+        <v>91473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700114</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700117</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>92147</v>
+        <v>92150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127700131</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127700145</v>
       </c>
       <c r="B6" t="n">
-        <v>78437</v>
+        <v>78438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127700138</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127700139</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91473</v>
+        <v>91476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127700118</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>127700116</v>
       </c>
       <c r="B16" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700114</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700117</v>
       </c>
       <c r="B3" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>92150</v>
+        <v>92157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127700131</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127700145</v>
       </c>
       <c r="B6" t="n">
-        <v>78438</v>
+        <v>78442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127700138</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127700139</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127700118</v>
       </c>
       <c r="B12" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>127700116</v>
       </c>
       <c r="B16" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>127700108</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>92157</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91482</v>
+        <v>91489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700114</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700117</v>
       </c>
       <c r="B3" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127700131</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127700145</v>
       </c>
       <c r="B6" t="n">
-        <v>78442</v>
+        <v>78444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127700138</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127700139</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91489</v>
+        <v>91491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127700118</v>
       </c>
       <c r="B12" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>127700116</v>
       </c>
       <c r="B16" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>127700108</v>
       </c>
       <c r="B18" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>92166</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,14 +1200,10 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,7 +1280,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,14 +1297,10 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1789,7 +1781,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1882,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1907,14 +1899,10 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1991,7 +1979,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,7 +2181,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700114</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700117</v>
       </c>
       <c r="B3" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127700131</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127700145</v>
       </c>
       <c r="B6" t="n">
-        <v>78444</v>
+        <v>78446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>127700138</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>127700139</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91491</v>
+        <v>91494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>127700118</v>
       </c>
       <c r="B12" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>127700116</v>
       </c>
       <c r="B16" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700114</v>
       </c>
       <c r="B2" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700117</v>
       </c>
       <c r="B3" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127700131</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127700145</v>
       </c>
       <c r="B6" t="n">
-        <v>78446</v>
+        <v>78447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>127700138</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>127700139</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91494</v>
+        <v>91496</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>127700118</v>
       </c>
       <c r="B12" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>127700116</v>
       </c>
       <c r="B16" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 12019-2023 artfynd.xlsx
+++ b/artfynd/A 12019-2023 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>127700124</v>
       </c>
       <c r="B4" t="n">
-        <v>92187</v>
+        <v>92191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127700126</v>
       </c>
       <c r="B7" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>127700125</v>
       </c>
       <c r="B8" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>127700105</v>
       </c>
       <c r="B11" t="n">
-        <v>91496</v>
+        <v>91500</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>127700144</v>
       </c>
       <c r="B13" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>127700127</v>
       </c>
       <c r="B14" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>127700143</v>
       </c>
       <c r="B15" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>127700111</v>
       </c>
       <c r="B17" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
